--- a/ig/DM-SEPTEMBRE-2025/CodeSystem-terminologie-sms.xlsx
+++ b/ig/DM-SEPTEMBRE-2025/CodeSystem-terminologie-sms.xlsx
@@ -40,7 +40,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2025-07</t>
+    <t>2025-09</t>
   </si>
   <si>
     <t>Name</t>
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-04T11:00:00+00:00</t>
+    <t>2025-09-08T13:13:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -124,7 +124,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>70056</t>
+    <t>70429</t>
   </si>
   <si>
     <t>Code</t>
